--- a/output/pdf_financials_xlsx/CFF.xlsx
+++ b/output/pdf_financials_xlsx/CFF.xlsx
@@ -2752,49 +2752,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>26.629</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>11.059</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>12.061</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>17.4161</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>10.0596</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>9.902900000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>12.6503</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>16.8604</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>16.3386</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.9195</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>6.354</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>8.438599999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.1907</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>3.6446</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>4.4333</v>
       </c>
     </row>
     <row r="35">
@@ -2856,49 +2856,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>26.629</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>11.059</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>12.061</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>17.4161</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>10.0596</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>9.902900000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>12.6503</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>16.8604</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>16.3386</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.9195</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>6.354</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>8.438599999999999</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>4.1907</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>3.6446</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>4.4333</v>
       </c>
     </row>
     <row r="37">
@@ -3480,49 +3480,49 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>30.714</v>
+        <v>4.085</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>17.375</v>
+        <v>6.316</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>20.119</v>
+        <v>8.058</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>24.6717</v>
+        <v>7.2556</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>20.7986</v>
+        <v>10.739</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>29.5677</v>
+        <v>19.6648</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>36.8665</v>
+        <v>24.2162</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>37.7861</v>
+        <v>20.9257</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>52.5173</v>
+        <v>36.1787</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>257.151</v>
+        <v>256.2315</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>28.6261</v>
+        <v>22.2721</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>33.6849</v>
+        <v>25.2463</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>26.8542</v>
+        <v>22.6635</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>23.3711</v>
+        <v>19.7265</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>20.686</v>
+        <v>16.2527</v>
       </c>
     </row>
     <row r="49">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -22651,7 +22651,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -25434,7 +25434,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E201" s="5" t="n">

--- a/output/pdf_financials_xlsx/CFF.xlsx
+++ b/output/pdf_financials_xlsx/CFF.xlsx
@@ -38784,7 +38784,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -39862,7 +39866,11 @@
           <t>Additions to intangible assets 17</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E367" s="5" t="n">
         <v>-0.075</v>
       </c>

--- a/output/pdf_financials_xlsx/CFF.xlsx
+++ b/output/pdf_financials_xlsx/CFF.xlsx
@@ -3064,19 +3064,19 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>2.301</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.6027</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.4519</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
@@ -3116,19 +3116,19 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>6.011</v>
+        <v>8.311999999999999</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>16.802</v>
+        <v>17.802</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>16.2426</v>
+        <v>16.8453</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>26.7156</v>
+        <v>27.1675</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>25.9294</v>
@@ -3480,19 +3480,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.085</v>
+        <v>1.784</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.316</v>
+        <v>5.866</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>8.058</v>
+        <v>7.058</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>7.2556</v>
+        <v>6.6529</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>10.739</v>
+        <v>10.2871</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>19.6648</v>
@@ -4342,19 +4342,19 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>4.172</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>9.141999999999999</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>23.783</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>27.0164</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>29.2279</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -4550,19 +4550,19 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>4.172</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.525</v>
+        <v>9.667</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>23.783</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>27.0164</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>29.2279</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0</v>
@@ -4914,19 +4914,19 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>9.923</v>
+        <v>5.751</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>30.604</v>
+        <v>21.462</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>43.714</v>
+        <v>19.931</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>43.8573</v>
+        <v>16.8409</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>48.1046</v>
+        <v>18.8767</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>70.4468</v>
@@ -7291,13 +7291,13 @@
         <v>0</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-14.3104</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-0.7679</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-0.0442</v>
       </c>
       <c r="O121" s="3" t="n">
         <v>0</v>
@@ -30647,7 +30647,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -32939,7 +32943,11 @@
           <t>Proceeds from public offering and private placement</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -33657,7 +33665,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
